--- a/reports/China_3.1.1_top_import_partners.xlsx
+++ b/reports/China_3.1.1_top_import_partners.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5351" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5390" uniqueCount="194">
   <si>
     <t>refYear</t>
   </si>
@@ -953,7 +953,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I1782"/>
+  <dimension ref="A1:I1795"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -52631,6 +52631,383 @@
         <v>5.447856771618873E-09</v>
       </c>
     </row>
+    <row r="1783" spans="1:9">
+      <c r="A1783" s="1">
+        <v>1787</v>
+      </c>
+      <c r="B1783">
+        <v>2025</v>
+      </c>
+      <c r="C1783" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1783" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1783">
+        <v>1</v>
+      </c>
+      <c r="F1783" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1783">
+        <v>120459718559.9</v>
+      </c>
+      <c r="H1783">
+        <v>0.3776983134661701</v>
+      </c>
+      <c r="I1783">
+        <v>0.3776983134661701</v>
+      </c>
+    </row>
+    <row r="1784" spans="1:9">
+      <c r="A1784" s="1">
+        <v>1782</v>
+      </c>
+      <c r="B1784">
+        <v>2025</v>
+      </c>
+      <c r="C1784" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1784" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1784">
+        <v>2</v>
+      </c>
+      <c r="F1784" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1784">
+        <v>100021440850</v>
+      </c>
+      <c r="H1784">
+        <v>0.3136146254626668</v>
+      </c>
+      <c r="I1784">
+        <v>0.3136146254626668</v>
+      </c>
+    </row>
+    <row r="1785" spans="1:9">
+      <c r="A1785" s="1">
+        <v>1786</v>
+      </c>
+      <c r="B1785">
+        <v>2025</v>
+      </c>
+      <c r="C1785" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1785" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1785">
+        <v>3</v>
+      </c>
+      <c r="F1785" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1785">
+        <v>67037765313.5</v>
+      </c>
+      <c r="H1785">
+        <v>0.2101951689755873</v>
+      </c>
+      <c r="I1785">
+        <v>0.2101951689755873</v>
+      </c>
+    </row>
+    <row r="1786" spans="1:9">
+      <c r="A1786" s="1">
+        <v>1793</v>
+      </c>
+      <c r="B1786">
+        <v>2025</v>
+      </c>
+      <c r="C1786" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1786" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1786">
+        <v>4</v>
+      </c>
+      <c r="F1786" t="s">
+        <v>36</v>
+      </c>
+      <c r="G1786">
+        <v>13558456380.596</v>
+      </c>
+      <c r="H1786">
+        <v>0.04251218722223116</v>
+      </c>
+      <c r="I1786">
+        <v>0.04251218722223116</v>
+      </c>
+    </row>
+    <row r="1787" spans="1:9">
+      <c r="A1787" s="1">
+        <v>1790</v>
+      </c>
+      <c r="B1787">
+        <v>2025</v>
+      </c>
+      <c r="C1787" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1787" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1787">
+        <v>5</v>
+      </c>
+      <c r="F1787" t="s">
+        <v>42</v>
+      </c>
+      <c r="G1787">
+        <v>9916492833</v>
+      </c>
+      <c r="H1787">
+        <v>0.0310929052740647</v>
+      </c>
+      <c r="I1787">
+        <v>0.0310929052740647</v>
+      </c>
+    </row>
+    <row r="1788" spans="1:9">
+      <c r="A1788" s="1">
+        <v>1791</v>
+      </c>
+      <c r="B1788">
+        <v>2025</v>
+      </c>
+      <c r="C1788" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1788" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1788">
+        <v>6</v>
+      </c>
+      <c r="F1788" t="s">
+        <v>51</v>
+      </c>
+      <c r="G1788">
+        <v>4799422264.213</v>
+      </c>
+      <c r="H1788">
+        <v>0.01504846363976714</v>
+      </c>
+      <c r="I1788">
+        <v>0.01504846363976714</v>
+      </c>
+    </row>
+    <row r="1789" spans="1:9">
+      <c r="A1789" s="1">
+        <v>1784</v>
+      </c>
+      <c r="B1789">
+        <v>2025</v>
+      </c>
+      <c r="C1789" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1789" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1789">
+        <v>7</v>
+      </c>
+      <c r="F1789" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1789">
+        <v>1857517867.706</v>
+      </c>
+      <c r="H1789">
+        <v>0.005824198945948584</v>
+      </c>
+      <c r="I1789">
+        <v>0.005824198945948584</v>
+      </c>
+    </row>
+    <row r="1790" spans="1:9">
+      <c r="A1790" s="1">
+        <v>1783</v>
+      </c>
+      <c r="B1790">
+        <v>2025</v>
+      </c>
+      <c r="C1790" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1790" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1790">
+        <v>8</v>
+      </c>
+      <c r="F1790" t="s">
+        <v>138</v>
+      </c>
+      <c r="G1790">
+        <v>503082294.588</v>
+      </c>
+      <c r="H1790">
+        <v>0.001577401445663284</v>
+      </c>
+      <c r="I1790">
+        <v>0.001577401445663284</v>
+      </c>
+    </row>
+    <row r="1791" spans="1:9">
+      <c r="A1791" s="1">
+        <v>1789</v>
+      </c>
+      <c r="B1791">
+        <v>2025</v>
+      </c>
+      <c r="C1791" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1791" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1791">
+        <v>9</v>
+      </c>
+      <c r="F1791" t="s">
+        <v>106</v>
+      </c>
+      <c r="G1791">
+        <v>270132789</v>
+      </c>
+      <c r="H1791">
+        <v>0.0008469943316900399</v>
+      </c>
+      <c r="I1791">
+        <v>0.0008469943316900399</v>
+      </c>
+    </row>
+    <row r="1792" spans="1:9">
+      <c r="A1792" s="1">
+        <v>1788</v>
+      </c>
+      <c r="B1792">
+        <v>2025</v>
+      </c>
+      <c r="C1792" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1792" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1792">
+        <v>10</v>
+      </c>
+      <c r="F1792" t="s">
+        <v>105</v>
+      </c>
+      <c r="G1792">
+        <v>256456990.313</v>
+      </c>
+      <c r="H1792">
+        <v>0.0008041142207190496</v>
+      </c>
+      <c r="I1792">
+        <v>0.0008041142207190496</v>
+      </c>
+    </row>
+    <row r="1793" spans="1:9">
+      <c r="A1793" s="1">
+        <v>1785</v>
+      </c>
+      <c r="B1793">
+        <v>2025</v>
+      </c>
+      <c r="C1793" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1793" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1793">
+        <v>11</v>
+      </c>
+      <c r="F1793" t="s">
+        <v>127</v>
+      </c>
+      <c r="G1793">
+        <v>197705981.05</v>
+      </c>
+      <c r="H1793">
+        <v>0.0006199019597379141</v>
+      </c>
+      <c r="I1793">
+        <v>0.0006199019597379141</v>
+      </c>
+    </row>
+    <row r="1794" spans="1:9">
+      <c r="A1794" s="1">
+        <v>1792</v>
+      </c>
+      <c r="B1794">
+        <v>2025</v>
+      </c>
+      <c r="C1794" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1794" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1794">
+        <v>12</v>
+      </c>
+      <c r="F1794" t="s">
+        <v>125</v>
+      </c>
+      <c r="G1794">
+        <v>52854825.03</v>
+      </c>
+      <c r="H1794">
+        <v>0.0001657249287234022</v>
+      </c>
+      <c r="I1794">
+        <v>0.0001657249287234022</v>
+      </c>
+    </row>
+    <row r="1795" spans="1:9">
+      <c r="A1795" s="1">
+        <v>1781</v>
+      </c>
+      <c r="B1795">
+        <v>2025</v>
+      </c>
+      <c r="C1795" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1795" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1795">
+        <v>13</v>
+      </c>
+      <c r="F1795" t="s">
+        <v>185</v>
+      </c>
+      <c r="G1795">
+        <v>40.514</v>
+      </c>
+      <c r="H1795">
+        <v>1.270305929210625E-10</v>
+      </c>
+      <c r="I1795">
+        <v>1.270305929210625E-10</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
